--- a/Teste/Teste7/Planilha_Testes_Unitarios.xlsx
+++ b/Teste/Teste7/Planilha_Testes_Unitarios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coman\OneDrive\Desktop\Formularios\Teste\Teste7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\camil\OneDrive\Área de Trabalho\AtividadesTeste\Teste\Teste7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540EEBB7-2C4C-43C0-B3B1-0BDC0C2C4ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A53937-AB78-478F-ABA2-E497A212A3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>ID do Teste</t>
   </si>
@@ -63,9 +63,6 @@
     <t>Descrição do Teste6</t>
   </si>
   <si>
-    <t>Calcula corretamente desconto de 10% em R$100</t>
-  </si>
-  <si>
     <t>Calcula corretamente desconto com valores decimais</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>Calcula corretamente preço com número em string</t>
   </si>
   <si>
-    <t xml:space="preserve"> Calcula corretamente desconto de 25% em R$300</t>
-  </si>
-  <si>
     <t>123.45, 12.5</t>
   </si>
   <si>
@@ -100,13 +94,34 @@
   </si>
   <si>
     <t>'200', '10'</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>João Pedro</t>
+  </si>
+  <si>
+    <t>Calcula corretamente desconto de 10% em R$200</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Calcula corretamente desconto de 25% em R$200</t>
+  </si>
+  <si>
+    <t>108.02</t>
+  </si>
+  <si>
+    <t>saida invalida</t>
+  </si>
+  <si>
+    <t>desconto invalido</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,19 +135,15 @@
       <family val="3"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFBCBEC4"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="JetBrains Mono"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -143,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -151,35 +162,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -490,136 +510,263 @@
     <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.42578125" customWidth="1"/>
     <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" ht="15.75">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2">
+    <row r="2" spans="1:9" ht="15.75">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
+      <c r="B2" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="C2" s="5">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3">
+      <c r="D2" s="4">
+        <v>180</v>
+      </c>
+      <c r="E2" s="4">
+        <v>180</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="6">
+        <v>45929</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3">
+        <v>300</v>
+      </c>
+      <c r="D3" s="4">
+        <v>225</v>
+      </c>
+      <c r="E3" s="4">
+        <v>225</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="6">
+        <v>45929</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="6">
+        <v>45929</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="7">
+        <v>-50</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="6">
+        <v>45929</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1">
-        <v>300</v>
-      </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="D6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="6">
+        <v>45929</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="7"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D7" s="4">
+        <v>50</v>
+      </c>
+      <c r="E7" s="4">
+        <v>50</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="6">
+        <v>45929</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="6">
+        <v>45929</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="D9" s="4">
+        <v>180</v>
+      </c>
+      <c r="E9" s="4">
+        <v>180</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="9" t="s">
+      <c r="G9" s="6">
+        <v>45929</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>22</v>
       </c>
+      <c r="I9" s="4"/>
     </row>
     <row r="14" spans="1:9">
       <c r="C14" s="1"/>
     </row>
     <row r="18" spans="3:3">
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>8</v>
       </c>
     </row>

--- a/Teste/Teste7/Planilha_Testes_Unitarios.xlsx
+++ b/Teste/Teste7/Planilha_Testes_Unitarios.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\camil\OneDrive\Área de Trabalho\AtividadesTeste\Teste\Teste7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\AtividadesTeste\Teste\Teste7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A53937-AB78-478F-ABA2-E497A212A3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E92FBC-C857-4790-B085-CF88F5F1F0CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testes Unitários" sheetId="1" r:id="rId1"/>
@@ -217,6 +217,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>2029698</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>95421</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{266E5D89-BEBF-2454-8284-BB14889EAA47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="200025" y="2000250"/>
+          <a:ext cx="6258798" cy="1228896"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -773,5 +822,6 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>